--- a/DemoDesign/Config/language.xlsx
+++ b/DemoDesign/Config/language.xlsx
@@ -1,96 +1,1225 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Think\Documents\git-repository\u-mini\DemoDesign\Config\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C75E32-D987-40DA-A615-70E2571F3090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="config" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="readme" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="config" sheetId="1" r:id="rId1"/>
+    <sheet name="readme" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="102">
+  <si>
+    <t>语言id</t>
+  </si>
+  <si>
+    <t>简体中文</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>日本語</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>JPN</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>lang_00001</t>
+  </si>
+  <si>
+    <t>选择武器</t>
+  </si>
+  <si>
+    <t>Select Weapon</t>
+  </si>
+  <si>
+    <t>武器を選択</t>
+  </si>
+  <si>
+    <t>무기 선택</t>
+  </si>
+  <si>
+    <t>lang_00002</t>
+  </si>
+  <si>
+    <t>进入游戏</t>
+  </si>
+  <si>
+    <t>Enter Game</t>
+  </si>
+  <si>
+    <t>ゲーム開始</t>
+  </si>
+  <si>
+    <t>게임 시작</t>
+  </si>
+  <si>
+    <t>lang_00003</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>設定</t>
+  </si>
+  <si>
+    <t>설정</t>
+  </si>
+  <si>
+    <t>第一行写字段注释(语言表第一行是语言选项文本值)</t>
+  </si>
+  <si>
+    <t>第二行写字段名(语言表第二行是语言字母代码)</t>
+  </si>
+  <si>
+    <t>第三行写字段类型 (id字段只支持 string)(支持 float string int bool 数组float[] string[] int[] bool[] 数组值用(;)分割)(语言表字段只能是string)</t>
+  </si>
+  <si>
+    <t>前三行的作用是固定的不可更改</t>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOR0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>33</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>34</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>한국인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>36</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>KOR1</t>
+  </si>
+  <si>
+    <t>KOR2</t>
+  </si>
+  <si>
+    <t>KOR3</t>
+  </si>
+  <si>
+    <t>KOR4</t>
+  </si>
+  <si>
+    <t>KOR5</t>
+  </si>
+  <si>
+    <t>KOR6</t>
+  </si>
+  <si>
+    <t>KOR7</t>
+  </si>
+  <si>
+    <t>KOR8</t>
+  </si>
+  <si>
+    <t>KOR9</t>
+  </si>
+  <si>
+    <t>KOR10</t>
+  </si>
+  <si>
+    <t>KOR11</t>
+  </si>
+  <si>
+    <t>KOR12</t>
+  </si>
+  <si>
+    <t>KOR13</t>
+  </si>
+  <si>
+    <t>KOR14</t>
+  </si>
+  <si>
+    <t>KOR15</t>
+  </si>
+  <si>
+    <t>KOR16</t>
+  </si>
+  <si>
+    <t>KOR17</t>
+  </si>
+  <si>
+    <t>KOR18</t>
+  </si>
+  <si>
+    <t>KOR19</t>
+  </si>
+  <si>
+    <t>KOR20</t>
+  </si>
+  <si>
+    <t>KOR21</t>
+  </si>
+  <si>
+    <t>KOR22</t>
+  </si>
+  <si>
+    <t>KOR23</t>
+  </si>
+  <si>
+    <t>KOR24</t>
+  </si>
+  <si>
+    <t>KOR25</t>
+  </si>
+  <si>
+    <t>KOR26</t>
+  </si>
+  <si>
+    <t>KOR27</t>
+  </si>
+  <si>
+    <t>KOR28</t>
+  </si>
+  <si>
+    <t>KOR29</t>
+  </si>
+  <si>
+    <t>KOR30</t>
+  </si>
+  <si>
+    <t>KOR31</t>
+  </si>
+  <si>
+    <t>KOR32</t>
+  </si>
+  <si>
+    <t>KOR33</t>
+  </si>
+  <si>
+    <t>KOR34</t>
+  </si>
+  <si>
+    <t>KOR35</t>
+  </si>
+  <si>
+    <t>KOR36</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color theme="0"/>
-      <sz val="16"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color theme="0"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="16"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Malgun Gothic"/>
-      <charset val="129"/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <family val="3"/>
-      <color theme="0"/>
-      <sz val="16"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color theme="0"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="16"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="等线"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="16"/>
-      <scheme val="minor"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -130,36 +1259,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -179,74 +1308,14 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -512,233 +1581,808 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="16.625" defaultRowHeight="28.5" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AO6"/>
+  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="28.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="20.375" customWidth="1" style="2" min="1" max="3"/>
-    <col width="20.375" customWidth="1" style="3" min="4" max="5"/>
-    <col width="16.625" customWidth="1" style="9" min="6" max="16384"/>
+    <col min="1" max="3" width="20.375" style="2" customWidth="1"/>
+    <col min="4" max="41" width="20.375" style="3" customWidth="1"/>
+    <col min="42" max="16384" width="16.625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.5" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>语言id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>简体中文</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>日本語</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>한국인</t>
-        </is>
+    <row r="1" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="S1" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="U1" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="V1" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="W1" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="X1" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y1" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z1" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA1" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB1" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC1" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD1" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE1" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AF1" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AG1" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH1" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="AI1" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ1" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK1" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL1" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="AM1" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN1" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO1" s="10" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="2" ht="28.5" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>ENG</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>JPN</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>KOR</t>
-        </is>
+    <row r="2" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE2" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ2" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM2" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="AN2" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO2" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
-    <row r="3" ht="28.5" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+    <row r="3" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="4" ht="28.5" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>lang_00001</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>选择武器</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Select Weapon</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>武器を選択</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>무기 선택</t>
-        </is>
+    <row r="4" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="T4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="W4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="X4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO4" s="11" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5" ht="28.5" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>lang_00002</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>进入游戏</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Enter Game</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>ゲーム開始</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>게임 시작</t>
-        </is>
+    <row r="5" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AM5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO5" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="6" ht="28.5" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>lang_00003</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>设置</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>設定</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
+    <row r="6" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="W6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO6" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" priority="5" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="89.375" defaultRowHeight="28.5" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="89.375" defaultRowHeight="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="66.125" customWidth="1" style="6" min="1" max="1"/>
-    <col width="89.375" customWidth="1" style="5" min="2" max="16384"/>
+    <col min="1" max="1" width="66.125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="89.375" style="5" customWidth="1"/>
+    <col min="3" max="16384" width="89.375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.5" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>第一行写字段注释(语言表第一行是语言选项文本值)</t>
-        </is>
+    <row r="1" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="2" ht="28.5" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>第二行写字段名(语言表第二行是语言字母代码)</t>
-        </is>
+    <row r="2" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" ht="28.5" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>第三行写字段类型 (id字段只支持 string)(支持 float string int bool 数组float[] string[] int[] bool[] 数组值用(;)分割)(语言表字段只能是string)</t>
-        </is>
+    <row r="3" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" ht="28.5" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>前三行的作用是固定的不可更改</t>
-        </is>
+    <row r="4" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
 </worksheet>
 </file>